--- a/results/Int Task Remove ACC 0.3/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7014257753449071</v>
+        <v>0.7135118469837531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7083979122575307</v>
+        <v>0.7135118469837531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7042697675158729</v>
+        <v>0.7153851662078513</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7055388030488678</v>
+        <v>0.7172660439507981</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7026796938402049</v>
+        <v>0.7099541715067708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.704911843801219</v>
+        <v>0.6883694285759751</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7046134812150915</v>
+        <v>0.688690466718648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7058825167480864</v>
+        <v>0.687459223779896</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7058825167480864</v>
+        <v>0.6820393679486976</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7445956590232803</v>
+        <v>0.6820393679486976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7395195168913006</v>
+        <v>0.6667731489585156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7287629489362379</v>
+        <v>0.6755430199067518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7268669541555941</v>
+        <v>0.6662555893257801</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7118235125630539</v>
+        <v>0.6596347246312239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6870168515188645</v>
+        <v>0.6721739095842019</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7292538548446128</v>
+        <v>0.6527003803128432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7267157837786229</v>
+        <v>0.6643747115828333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.736248667313782</v>
+        <v>0.6796747449994431</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.745139474563595</v>
+        <v>0.6787191890902726</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7489465811625797</v>
+        <v>0.6726345814171825</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.692583899559219</v>
+        <v>0.6729405025221584</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.692583899559219</v>
+        <v>0.6752709132282037</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6929124962207406</v>
+        <v>0.6806454179463106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6715087599255287</v>
+        <v>0.6806454179463106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6737409098865427</v>
+        <v>0.6717546106964976</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6718222395493532</v>
+        <v>0.6717546106964976</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6730912750823481</v>
+        <v>0.6717546106964976</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6771967442674601</v>
+        <v>0.6678078704072052</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6696052066260363</v>
+        <v>0.6737413077033241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6652316089301911</v>
+        <v>0.6648051493404198</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6804146842130389</v>
+        <v>0.6610207182979807</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6722339799182089</v>
+        <v>0.6481680537211783</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6709725029040625</v>
+        <v>0.651348201072514</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6774008242763713</v>
+        <v>0.6603826201804497</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6850225959931894</v>
+        <v>0.6700853714813105</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6580593701764715</v>
+        <v>0.6637326352974874</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6580593701764715</v>
+        <v>0.6660025778527441</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.624308992250529</v>
+        <v>0.6634796238244514</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6195841223366166</v>
+        <v>0.6304508855401556</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6310583517655108</v>
+        <v>0.5895585029358879</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6596040927390481</v>
+        <v>0.5815854590010024</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6587316805372118</v>
+        <v>0.5815854590010024</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6349410435529812</v>
+        <v>0.5835570389701319</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6320668173066213</v>
+        <v>0.5835570389701319</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6490062536798052</v>
+        <v>0.5851319956081027</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6566129083589262</v>
+        <v>0.5862498607641264</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6167894594465573</v>
+        <v>0.5432609837213372</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6106030106774024</v>
+        <v>0.5449871107362793</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6258580907977023</v>
+        <v>0.5402507041357032</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6323051095587416</v>
+        <v>0.5359073405152524</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5782350460671833</v>
+        <v>0.5270618843785306</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5639056855974413</v>
+        <v>0.5158975542224273</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5260955874162596</v>
+        <v>0.5099943510017027</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5260955874162596</v>
+        <v>0.5109423483920246</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5244526041086517</v>
+        <v>0.5159958149674586</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4908573747274955</v>
+        <v>0.530374504718107</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5164190920229779</v>
+        <v>0.5626704644908741</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5014814696943176</v>
+        <v>0.5556832105405535</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5087897617873113</v>
+        <v>0.5588402845185622</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5031168944830768</v>
+        <v>0.5588402845185622</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5069995862705472</v>
+        <v>0.5194926244768709</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5094505354613879</v>
+        <v>0.5169847874862753</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5110254920993587</v>
+        <v>0.5266915169549512</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5065989847715736</v>
+        <v>0.5335805101602407</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5069049058765495</v>
+        <v>0.5329006412806518</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4706391324411629</v>
+        <v>0.5164560889836577</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4706391324411629</v>
+        <v>0.528130420253648</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4706391324411629</v>
+        <v>0.5100126505736517</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5244971595881801</v>
+        <v>0.5017488025714877</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5238097321897427</v>
+        <v>0.5112136594370097</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5159954171506771</v>
+        <v>0.5032784080963671</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5520686472638162</v>
+        <v>0.5000982607450313</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5349784383304426</v>
+        <v>0.5000907022261827</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5393595945451363</v>
+        <v>0.5013597377591776</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5706785163025317</v>
+        <v>0.5041659373359005</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5701271422433685</v>
+        <v>0.4990746781662238</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5795315309581019</v>
+        <v>0.4993957163088968</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5283472303995671</v>
+        <v>0.5006496348041946</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.592134764412902</v>
+        <v>0.4984326018808777</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5852720271151918</v>
+        <v>0.5000075585188486</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5909675699759719</v>
+        <v>0.5009555559091705</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5982348869404707</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.593615040656875</v>
+        <v>0.4993730407523511</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5468763426316375</v>
+        <v>0.4996865203761756</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5468914596693347</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5468914596693347</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5546150724822176</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5778925258183092</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4983104721289563</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
